--- a/docs/PPG/Prêmios.xlsx
+++ b/docs/PPG/Prêmios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62776408-8A72-934D-AAD1-219701ED0482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB083101-AB45-7B4B-A3A7-E9E438079AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="680" windowWidth="28520" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
+    <workbookView xWindow="920" yWindow="680" windowWidth="28520" windowHeight="18960" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
   <sheets>
     <sheet name="Prêmios" sheetId="18" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="121">
   <si>
     <t>Certificamos que SAMANTHA GOMES DE ALEGRIA, participou do “1o CONGRESSO ONLINE INTERNACIONAL DE FISIOTERAPIA MÚSCULOESQUELÉTICA”, de 17 a 18 de Abril de 2021, realizado pelo “Grupo Acolher e Cuidar”, com carga horária de 180 horas</t>
   </si>
@@ -368,6 +368,39 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/159IW8t1qWDiMdCxLoWjvhYFVHCqQOlVv</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>O Colegiado do CONSELHO REGIONAL DE FISIOTERAPIA E TERAPIA OCUPACIONAL DA 2ª REGIÃO – CREFITO-2 confere o presente certificado a DRA. ANA CAROLINA SEBASTIÃO DA SILVA em reconhecimento ao Prêmio de Apresentações Orais Temáticas – Fisioterapia Respiratória – Adulto (Ambulatorial e Domiciliar), concedido durante o XXII SIFR pela ASSOBRAFIR, pela apresentação do trabalho intitulado “SUPERVISED VERSUS HOME-BASED PULMONARY REHABILITATION IN POST INTENSIVE CARE SYNDROME: A SINGLE-BLIND RANDOMIZED CONTROLLED NON-INFERIORITY TRIAL COMPARING FUNCTIONAL OUTCOMES AND MUSCLE PERFORMANCE”. A premiação reconhece a relevância científica do estudo apresentado e sua contribuição para o desenvolvimento e a disseminação do conhecimento na área da Fisioterapia. Dr. Wilen Heil e Silva Presidente do Crefito - 2</t>
+  </si>
+  <si>
+    <t>O Colegiado do CONSELHO REGIONAL DE FISIOTERAPIA E TERAPIA OCUPACIONAL DA 2ª REGIÃO – CREFITO-2 confere o presente certificado a DRA. VIVIAN CORRÊA DE OLIVEIRA MARÇAL em reconhecimento ao Prêmio de Pôster Temático (Impresso) Fisioterapia em Terapia Intensiva – Pediatria, concedido durante o XXII SIFR pela ASSOBRAFIR, pela apresentação do trabalho intitulado “Acurácia da Fração de Espessamento do Diafragma para Predizer o Desfecho da Extubação em Pacientes Pediátricos”. A premiação reconhece a relevância científica do estudo apresentado e sua contribuição para o desenvolvimento e a disseminação do conhecimento na área da Fisioterapia. Dr. Wilen Heil e Silva Presidente do Crefito - 2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1chjtmTTpE_b_fEdKW5ecYBe57saVR0zd</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1myPM27unAyT6eM_-9Do26i-IY-To3Yv3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aPwTxQJyDy9BQkaiJi9QUvI_EWMcPgV7</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_hxSWGxgDMQj_8HrF_4R4mvXCH63_BG3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15APNilnHRG-c92NQ4vUJNce4YyzHv2rO</t>
+  </si>
+  <si>
+    <t>Certificamos que o trabalho intitulado SUPERVISED VERSUS HOME-BASED PULMONARY REHABILITATION IN POST INTENSIVE CARE SYNDROME: A SINGLE-BLIND RANDOMIZED CONTROLLED NON-INFERIORITY TRIAL COMPARING FUNCTIONAL OUTCOMES AND MUSCLE PERFORMANCE de autoria de ANA CAROLINA SEBASTIÃO DA SILVA; FLAVIA MAZZOLI DA ROCHA; ARTHUR DE SÁ FERREIRA; AGNALDO JOSÉ LOPES; LUIS FELIPE DA FONSECA REIS foi apresentado na forma de MELHORES RESUMOS - APRESENTAÇÃO ORAL no XXII Simpósio Internacional de Fisioterapia Respiratória, Cardiovascular e de Terapia Intensiva (SIFR), promovido pela ASSOBRAFIR, no período de 13 a 15 de agosto de 2026, no Centro de Convenções de Natal/RN. Natal/RN, 15 de agosto de 2026.</t>
+  </si>
+  <si>
+    <t>Certificamos que o trabalho intitulado Efeitos do treinamento muscular inspiratório de moderada e alta intensidades em indivíduos com apneia obstrutiva do sono: Revisão sistemática e meta-análise de autoria de JENNIFER MARIA DE ALMEIDA AGUIAR; LEANDRO MIRANDA DE AZEREDO; FLAVIA MAZZOLI DA ROCHA; ARTHUR DE SÁ FERREIRA; CLARA PINTO DINIZ; LUIS FELIPE DA FONSECA REIS foi apresentado na forma de MELHORES RESUMOS - APRESENTAÇÃO ORAL no XXII Simpósio Internacional de Fisioterapia Respiratória, Cardiovascular e de Terapia Intensiva (SIFR), promovido pela ASSOBRAFIR, no período de 13 a 15 de agosto de 2026, no Centro de Convenções de Natal/RN. Natal/RN, 15 de agosto de 2026.</t>
+  </si>
+  <si>
+    <t>Certificamos que o trabalho intitulado DOR, DRIVE RESPIRATORIO E ASSINCRONIAS COMO PREDITORES DE DESFECHOS EM PACIENTES VENTILADOS MECANICAMENTE: COORTE PROSPECTIVA MULTICENTRICA de autoria de RAÍSA MARTINS BORGHI; ANDRÉIA ROSÂNGELA OLIVEIRA DE MORAES DO CARMO; MARCELLY BERMUDES DE CARVALHO; BRUNO CURTY BERGAMINI; ANTUANI RAFAEL BAPTISTELLA; ARTHUR DE SÁ FERREIRA; AGNALDO JOSÉ LOPES; LUIS FELIPE DA FONSECA REIS foi apresentado na forma de MELHORES RESUMOS - APRESENTAÇÃO ORAL no XXII Simpósio Internacional de Fisioterapia Respiratória, Cardiovascular e de Terapia Intensiva (SIFR), promovido pela ASSOBRAFIR, no período de 13 a 15 de agosto de 2026, no Centro de Convenções de Natal/RN. Natal/RN, 15 de agosto de 2026.</t>
   </si>
 </sst>
 </file>
@@ -767,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240CACD3-9479-9B42-828C-5ED4A3697A49}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -1445,6 +1478,76 @@
       </c>
       <c r="D48" s="4" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A51" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1494,6 +1597,11 @@
     <hyperlink ref="D46" r:id="rId43" xr:uid="{197E14B1-1B93-8D46-8B9A-BB038810B373}"/>
     <hyperlink ref="D47" r:id="rId44" xr:uid="{6B4C376A-2731-C845-9725-442EFCA73F62}"/>
     <hyperlink ref="D48" r:id="rId45" xr:uid="{CC007CC7-32B1-2B44-9076-125828D11640}"/>
+    <hyperlink ref="D49" r:id="rId46" xr:uid="{E79968EB-A1A1-FF4B-B337-950D0DA2D6E8}"/>
+    <hyperlink ref="D50" r:id="rId47" xr:uid="{137653C6-EE83-7A46-951A-669450BD850C}"/>
+    <hyperlink ref="D51" r:id="rId48" xr:uid="{DE7F77EC-5C52-B74C-830C-F7E321321519}"/>
+    <hyperlink ref="D52" r:id="rId49" xr:uid="{FC2508F1-E2A0-F547-854C-1C2C10C57589}"/>
+    <hyperlink ref="D53" r:id="rId50" xr:uid="{1B2F4ACF-5CD3-EF46-B6A8-DF391C88EDBC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
